--- a/Unity/Assets/Config/Excel/BattlePassConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BattlePassConfig.xlsx
@@ -1403,7 +1403,7 @@
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="B14" s="2">
-        <v>10002002</v>
+        <v>10000011</v>
       </c>
       <c r="C14" s="2">
         <f t="shared" si="0"/>
